--- a/artfynd/A 11569-2024 artfynd.xlsx
+++ b/artfynd/A 11569-2024 artfynd.xlsx
@@ -1800,7 +1800,7 @@
         <v>121290064</v>
       </c>
       <c r="B11" t="n">
-        <v>57364</v>
+        <v>57367</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1934,10 +1934,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121288025</v>
+        <v>121290321</v>
       </c>
       <c r="B12" t="n">
-        <v>97028</v>
+        <v>57367</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1946,40 +1946,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1988,10 +1979,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>619193</v>
+        <v>619129</v>
       </c>
       <c r="R12" t="n">
-        <v>6568180</v>
+        <v>6568209</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2023,7 +2014,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2033,7 +2024,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2048,6 +2039,26 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Tallskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2065,10 +2076,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121288667</v>
+        <v>121288727</v>
       </c>
       <c r="B13" t="n">
-        <v>57364</v>
+        <v>92008</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2081,27 +2092,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2110,10 +2125,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>619177</v>
+        <v>619130</v>
       </c>
       <c r="R13" t="n">
-        <v>6568180</v>
+        <v>6568178</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2145,7 +2160,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2155,7 +2170,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2170,26 +2185,6 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Tallskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2207,10 +2202,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121290012</v>
+        <v>121289808</v>
       </c>
       <c r="B14" t="n">
-        <v>57364</v>
+        <v>8432</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2219,31 +2214,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2252,10 +2247,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>619161</v>
+        <v>619177</v>
       </c>
       <c r="R14" t="n">
-        <v>6568179</v>
+        <v>6568180</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2287,7 +2282,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2297,7 +2292,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2326,12 +2321,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stump # Pinus sylvestris</t>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2349,10 +2344,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121289808</v>
+        <v>121290012</v>
       </c>
       <c r="B15" t="n">
-        <v>8432</v>
+        <v>57367</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2361,31 +2356,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2394,10 +2389,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>619177</v>
+        <v>619161</v>
       </c>
       <c r="R15" t="n">
-        <v>6568180</v>
+        <v>6568179</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2429,7 +2424,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2439,7 +2434,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2468,12 +2463,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Vedyta på död ved</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
+          <t>Stump # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2491,10 +2486,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121288727</v>
+        <v>121288025</v>
       </c>
       <c r="B16" t="n">
-        <v>91998</v>
+        <v>97038</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2503,25 +2498,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>221946</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2531,7 +2526,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>619130</v>
+        <v>619193</v>
       </c>
       <c r="R16" t="n">
-        <v>6568178</v>
+        <v>6568180</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2617,10 +2617,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121290321</v>
+        <v>121290254</v>
       </c>
       <c r="B17" t="n">
-        <v>57364</v>
+        <v>4772</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2629,31 +2629,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2662,10 +2662,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>619129</v>
+        <v>619160</v>
       </c>
       <c r="R17" t="n">
-        <v>6568209</v>
+        <v>6568210</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2726,22 +2726,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2759,10 +2759,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121290254</v>
+        <v>121288667</v>
       </c>
       <c r="B18" t="n">
-        <v>4772</v>
+        <v>57367</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2771,31 +2771,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2804,10 +2804,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>619160</v>
+        <v>619177</v>
       </c>
       <c r="R18" t="n">
-        <v>6568210</v>
+        <v>6568180</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2868,22 +2868,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 11569-2024 artfynd.xlsx
+++ b/artfynd/A 11569-2024 artfynd.xlsx
@@ -1934,7 +1934,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121290321</v>
+        <v>121290012</v>
       </c>
       <c r="B12" t="n">
         <v>57367</v>
@@ -1970,7 +1970,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1979,10 +1979,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>619129</v>
+        <v>619161</v>
       </c>
       <c r="R12" t="n">
-        <v>6568209</v>
+        <v>6568179</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Stump # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2076,10 +2076,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121288727</v>
+        <v>121290321</v>
       </c>
       <c r="B13" t="n">
-        <v>92008</v>
+        <v>57367</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2092,31 +2092,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2125,10 +2121,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>619130</v>
+        <v>619129</v>
       </c>
       <c r="R13" t="n">
-        <v>6568178</v>
+        <v>6568209</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2160,7 +2156,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2170,7 +2166,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2185,6 +2181,26 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Tallskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2202,10 +2218,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121289808</v>
+        <v>121288025</v>
       </c>
       <c r="B14" t="n">
-        <v>8432</v>
+        <v>97038</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2218,27 +2234,36 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>221946</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2247,7 +2272,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>619177</v>
+        <v>619193</v>
       </c>
       <c r="R14" t="n">
         <v>6568180</v>
@@ -2282,7 +2307,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2292,7 +2317,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2307,26 +2332,6 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Tallskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2344,10 +2349,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121290012</v>
+        <v>121289808</v>
       </c>
       <c r="B15" t="n">
-        <v>57367</v>
+        <v>8432</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2356,31 +2361,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2389,10 +2394,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>619161</v>
+        <v>619177</v>
       </c>
       <c r="R15" t="n">
-        <v>6568179</v>
+        <v>6568180</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2424,7 +2429,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2434,7 +2439,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2463,12 +2468,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stump # Pinus sylvestris</t>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2486,10 +2491,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121288025</v>
+        <v>121288667</v>
       </c>
       <c r="B16" t="n">
-        <v>97038</v>
+        <v>57367</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2498,40 +2503,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2540,7 +2536,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>619193</v>
+        <v>619177</v>
       </c>
       <c r="R16" t="n">
         <v>6568180</v>
@@ -2575,7 +2571,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2585,7 +2581,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2600,6 +2596,26 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Tallskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2759,10 +2775,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121288667</v>
+        <v>121288727</v>
       </c>
       <c r="B18" t="n">
-        <v>57367</v>
+        <v>92008</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2775,27 +2791,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2804,10 +2824,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>619177</v>
+        <v>619130</v>
       </c>
       <c r="R18" t="n">
-        <v>6568180</v>
+        <v>6568178</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2839,7 +2859,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2849,7 +2869,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2864,26 +2884,6 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Tallskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 11569-2024 artfynd.xlsx
+++ b/artfynd/A 11569-2024 artfynd.xlsx
@@ -1797,7 +1797,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121290064</v>
+        <v>121290012</v>
       </c>
       <c r="B11" t="n">
         <v>57367</v>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>619160</v>
+        <v>619161</v>
       </c>
       <c r="R11" t="n">
-        <v>6568210</v>
+        <v>6568179</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1906,17 +1906,22 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stump # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1934,10 +1939,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121290012</v>
+        <v>121290254</v>
       </c>
       <c r="B12" t="n">
-        <v>57367</v>
+        <v>4772</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1946,31 +1951,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1979,10 +1984,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>619161</v>
+        <v>619160</v>
       </c>
       <c r="R12" t="n">
-        <v>6568179</v>
+        <v>6568210</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2014,7 +2019,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2024,7 +2029,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2043,22 +2048,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stump # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2218,10 +2223,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121288025</v>
+        <v>121288667</v>
       </c>
       <c r="B14" t="n">
-        <v>97038</v>
+        <v>57367</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2230,40 +2235,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2272,7 +2268,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>619193</v>
+        <v>619177</v>
       </c>
       <c r="R14" t="n">
         <v>6568180</v>
@@ -2307,7 +2303,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2317,7 +2313,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2332,6 +2328,26 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Tallskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2349,10 +2365,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121289808</v>
+        <v>121288727</v>
       </c>
       <c r="B15" t="n">
-        <v>8432</v>
+        <v>92020</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2361,31 +2377,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2394,10 +2414,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>619177</v>
+        <v>619130</v>
       </c>
       <c r="R15" t="n">
-        <v>6568180</v>
+        <v>6568178</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2429,7 +2449,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2439,7 +2459,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2454,26 +2474,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Tallskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2491,7 +2491,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121288667</v>
+        <v>121290064</v>
       </c>
       <c r="B16" t="n">
         <v>57367</v>
@@ -2536,10 +2536,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>619177</v>
+        <v>619160</v>
       </c>
       <c r="R16" t="n">
-        <v>6568180</v>
+        <v>6568210</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2600,22 +2600,17 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2633,10 +2628,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121290254</v>
+        <v>121289808</v>
       </c>
       <c r="B17" t="n">
-        <v>4772</v>
+        <v>8432</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2649,27 +2644,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102306</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2678,10 +2673,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>619160</v>
+        <v>619177</v>
       </c>
       <c r="R17" t="n">
-        <v>6568210</v>
+        <v>6568180</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2713,7 +2708,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2723,7 +2718,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2742,22 +2737,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2775,10 +2770,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121288727</v>
+        <v>121288025</v>
       </c>
       <c r="B18" t="n">
-        <v>92008</v>
+        <v>97051</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2787,25 +2782,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>221946</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2815,7 +2810,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>619130</v>
+        <v>619193</v>
       </c>
       <c r="R18" t="n">
-        <v>6568178</v>
+        <v>6568180</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2859,7 +2859,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 11569-2024 artfynd.xlsx
+++ b/artfynd/A 11569-2024 artfynd.xlsx
@@ -1797,10 +1797,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121290012</v>
+        <v>121290254</v>
       </c>
       <c r="B11" t="n">
-        <v>57367</v>
+        <v>4772</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1809,31 +1809,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>619161</v>
+        <v>619160</v>
       </c>
       <c r="R11" t="n">
-        <v>6568179</v>
+        <v>6568210</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1906,22 +1906,22 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stump # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121290254</v>
+        <v>121288667</v>
       </c>
       <c r="B12" t="n">
-        <v>4772</v>
+        <v>57367</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1951,31 +1951,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>619160</v>
+        <v>619177</v>
       </c>
       <c r="R12" t="n">
-        <v>6568210</v>
+        <v>6568180</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2048,22 +2048,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2081,7 +2081,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121290321</v>
+        <v>121290064</v>
       </c>
       <c r="B13" t="n">
         <v>57367</v>
@@ -2117,7 +2117,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>619129</v>
+        <v>619160</v>
       </c>
       <c r="R13" t="n">
-        <v>6568209</v>
+        <v>6568210</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2190,22 +2190,17 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2223,7 +2218,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121288667</v>
+        <v>121290012</v>
       </c>
       <c r="B14" t="n">
         <v>57367</v>
@@ -2268,10 +2263,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>619177</v>
+        <v>619161</v>
       </c>
       <c r="R14" t="n">
-        <v>6568180</v>
+        <v>6568179</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2303,7 +2298,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2313,7 +2308,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2342,12 +2337,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Stump # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2368,7 +2363,7 @@
         <v>121288727</v>
       </c>
       <c r="B15" t="n">
-        <v>92020</v>
+        <v>92021</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2491,10 +2486,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121290064</v>
+        <v>121289808</v>
       </c>
       <c r="B16" t="n">
-        <v>57367</v>
+        <v>8432</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2503,31 +2498,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2536,10 +2531,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>619160</v>
+        <v>619177</v>
       </c>
       <c r="R16" t="n">
-        <v>6568210</v>
+        <v>6568180</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2571,7 +2566,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2581,7 +2576,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2600,17 +2595,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2628,10 +2628,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121289808</v>
+        <v>121290321</v>
       </c>
       <c r="B17" t="n">
-        <v>8432</v>
+        <v>57367</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2640,31 +2640,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>619177</v>
+        <v>619129</v>
       </c>
       <c r="R17" t="n">
-        <v>6568180</v>
+        <v>6568209</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Vedyta på död ved</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2773,7 +2773,7 @@
         <v>121288025</v>
       </c>
       <c r="B18" t="n">
-        <v>97051</v>
+        <v>97052</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 11569-2024 artfynd.xlsx
+++ b/artfynd/A 11569-2024 artfynd.xlsx
@@ -1797,10 +1797,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121290254</v>
+        <v>121288667</v>
       </c>
       <c r="B11" t="n">
-        <v>4772</v>
+        <v>57370</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1809,31 +1809,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>619160</v>
+        <v>619177</v>
       </c>
       <c r="R11" t="n">
-        <v>6568210</v>
+        <v>6568180</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1906,22 +1906,22 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121288667</v>
+        <v>121290321</v>
       </c>
       <c r="B12" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>619177</v>
+        <v>619129</v>
       </c>
       <c r="R12" t="n">
-        <v>6568180</v>
+        <v>6568209</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2081,10 +2081,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121290064</v>
+        <v>121288727</v>
       </c>
       <c r="B13" t="n">
-        <v>57367</v>
+        <v>92024</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2097,27 +2097,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2126,10 +2130,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>619160</v>
+        <v>619130</v>
       </c>
       <c r="R13" t="n">
-        <v>6568210</v>
+        <v>6568178</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2161,7 +2165,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2171,7 +2175,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2186,21 +2190,6 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Tallskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2218,10 +2207,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121290012</v>
+        <v>121290254</v>
       </c>
       <c r="B14" t="n">
-        <v>57367</v>
+        <v>4775</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2230,31 +2219,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2263,10 +2252,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>619161</v>
+        <v>619160</v>
       </c>
       <c r="R14" t="n">
-        <v>6568179</v>
+        <v>6568210</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2298,7 +2287,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2308,7 +2297,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2327,22 +2316,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stump # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2360,10 +2349,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121288727</v>
+        <v>121289808</v>
       </c>
       <c r="B15" t="n">
-        <v>92021</v>
+        <v>8435</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2372,35 +2361,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2409,10 +2394,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>619130</v>
+        <v>619177</v>
       </c>
       <c r="R15" t="n">
-        <v>6568178</v>
+        <v>6568180</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2444,7 +2429,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2454,7 +2439,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2469,6 +2454,26 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Tallskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2486,10 +2491,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121289808</v>
+        <v>121288025</v>
       </c>
       <c r="B16" t="n">
-        <v>8432</v>
+        <v>97055</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2502,27 +2507,36 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>221946</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2531,7 +2545,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>619177</v>
+        <v>619193</v>
       </c>
       <c r="R16" t="n">
         <v>6568180</v>
@@ -2566,7 +2580,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2576,7 +2590,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2591,26 +2605,6 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Tallskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2628,10 +2622,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121290321</v>
+        <v>121290064</v>
       </c>
       <c r="B17" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2664,7 +2658,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2673,10 +2667,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>619129</v>
+        <v>619160</v>
       </c>
       <c r="R17" t="n">
-        <v>6568209</v>
+        <v>6568210</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2708,7 +2702,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2718,7 +2712,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2737,22 +2731,17 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2770,10 +2759,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121288025</v>
+        <v>121290012</v>
       </c>
       <c r="B18" t="n">
-        <v>97052</v>
+        <v>57370</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2782,40 +2771,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2824,10 +2804,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>619193</v>
+        <v>619161</v>
       </c>
       <c r="R18" t="n">
-        <v>6568180</v>
+        <v>6568179</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2859,7 +2839,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2869,7 +2849,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2884,6 +2864,26 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Tallskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Stump # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 11569-2024 artfynd.xlsx
+++ b/artfynd/A 11569-2024 artfynd.xlsx
@@ -1797,10 +1797,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121288667</v>
+        <v>121288025</v>
       </c>
       <c r="B11" t="n">
-        <v>57370</v>
+        <v>97055</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1809,31 +1809,40 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>221946</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1842,7 +1851,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>619177</v>
+        <v>619193</v>
       </c>
       <c r="R11" t="n">
         <v>6568180</v>
@@ -1877,7 +1886,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1887,7 +1896,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1902,26 +1911,6 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Tallskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1939,7 +1928,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121290321</v>
+        <v>121288667</v>
       </c>
       <c r="B12" t="n">
         <v>57370</v>
@@ -1975,7 +1964,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1984,10 +1973,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>619129</v>
+        <v>619177</v>
       </c>
       <c r="R12" t="n">
-        <v>6568209</v>
+        <v>6568180</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2019,7 +2008,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2029,7 +2018,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2081,10 +2070,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121288727</v>
+        <v>121290012</v>
       </c>
       <c r="B13" t="n">
-        <v>92024</v>
+        <v>57370</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2097,31 +2086,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2130,10 +2115,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>619130</v>
+        <v>619161</v>
       </c>
       <c r="R13" t="n">
-        <v>6568178</v>
+        <v>6568179</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2165,7 +2150,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2175,7 +2160,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2190,6 +2175,26 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Tallskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Stump # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2207,10 +2212,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121290254</v>
+        <v>121288727</v>
       </c>
       <c r="B14" t="n">
-        <v>4775</v>
+        <v>92024</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2219,31 +2224,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102306</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2252,10 +2261,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>619160</v>
+        <v>619130</v>
       </c>
       <c r="R14" t="n">
-        <v>6568210</v>
+        <v>6568178</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2287,7 +2296,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2297,7 +2306,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2312,26 +2321,6 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Tallskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2349,10 +2338,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121289808</v>
+        <v>121290254</v>
       </c>
       <c r="B15" t="n">
-        <v>8435</v>
+        <v>4775</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2365,27 +2354,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>102306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2394,10 +2383,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>619177</v>
+        <v>619160</v>
       </c>
       <c r="R15" t="n">
-        <v>6568180</v>
+        <v>6568210</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2429,7 +2418,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2439,7 +2428,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2458,22 +2447,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Vedyta på död ved</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2491,10 +2480,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121288025</v>
+        <v>121290321</v>
       </c>
       <c r="B16" t="n">
-        <v>97055</v>
+        <v>57370</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2503,40 +2492,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2545,10 +2525,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>619193</v>
+        <v>619129</v>
       </c>
       <c r="R16" t="n">
-        <v>6568180</v>
+        <v>6568209</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2580,7 +2560,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2590,7 +2570,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2605,6 +2585,26 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Tallskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2622,10 +2622,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121290064</v>
+        <v>121289808</v>
       </c>
       <c r="B17" t="n">
-        <v>57370</v>
+        <v>8435</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2634,31 +2634,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2667,10 +2667,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>619160</v>
+        <v>619177</v>
       </c>
       <c r="R17" t="n">
-        <v>6568210</v>
+        <v>6568180</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2702,7 +2702,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2731,17 +2731,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2759,7 +2764,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121290012</v>
+        <v>121290064</v>
       </c>
       <c r="B18" t="n">
         <v>57370</v>
@@ -2804,10 +2809,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>619161</v>
+        <v>619160</v>
       </c>
       <c r="R18" t="n">
-        <v>6568179</v>
+        <v>6568210</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2839,7 +2844,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2849,7 +2854,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2868,22 +2873,17 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stump # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 11569-2024 artfynd.xlsx
+++ b/artfynd/A 11569-2024 artfynd.xlsx
@@ -1797,10 +1797,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121288025</v>
+        <v>121290012</v>
       </c>
       <c r="B11" t="n">
-        <v>97055</v>
+        <v>57371</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1809,40 +1809,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1851,10 +1842,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>619193</v>
+        <v>619161</v>
       </c>
       <c r="R11" t="n">
-        <v>6568180</v>
+        <v>6568179</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1886,7 +1877,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1896,7 +1887,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1911,6 +1902,26 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Tallskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Stump # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1931,7 +1942,7 @@
         <v>121288667</v>
       </c>
       <c r="B12" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2070,10 +2081,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121290012</v>
+        <v>121290064</v>
       </c>
       <c r="B13" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2115,10 +2126,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>619161</v>
+        <v>619160</v>
       </c>
       <c r="R13" t="n">
-        <v>6568179</v>
+        <v>6568210</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2150,7 +2161,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2160,7 +2171,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2179,22 +2190,17 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stump # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2212,10 +2218,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121288727</v>
+        <v>121289808</v>
       </c>
       <c r="B14" t="n">
-        <v>92024</v>
+        <v>8435</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2224,35 +2230,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2261,10 +2263,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>619130</v>
+        <v>619177</v>
       </c>
       <c r="R14" t="n">
-        <v>6568178</v>
+        <v>6568180</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2296,7 +2298,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2306,7 +2308,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2321,6 +2323,26 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Tallskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2338,10 +2360,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121290254</v>
+        <v>121288727</v>
       </c>
       <c r="B15" t="n">
-        <v>4775</v>
+        <v>92030</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2350,31 +2372,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102306</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2383,10 +2409,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>619160</v>
+        <v>619130</v>
       </c>
       <c r="R15" t="n">
-        <v>6568210</v>
+        <v>6568178</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2418,7 +2444,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2428,7 +2454,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2443,26 +2469,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Tallskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2480,10 +2486,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121290321</v>
+        <v>121288025</v>
       </c>
       <c r="B16" t="n">
-        <v>57370</v>
+        <v>97061</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2492,31 +2498,40 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>221946</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2525,10 +2540,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>619129</v>
+        <v>619193</v>
       </c>
       <c r="R16" t="n">
-        <v>6568209</v>
+        <v>6568180</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2560,7 +2575,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2570,7 +2585,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2585,26 +2600,6 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Tallskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2622,10 +2617,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121289808</v>
+        <v>121290254</v>
       </c>
       <c r="B17" t="n">
-        <v>8435</v>
+        <v>4775</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2638,27 +2633,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>102306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2667,10 +2662,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>619177</v>
+        <v>619160</v>
       </c>
       <c r="R17" t="n">
-        <v>6568180</v>
+        <v>6568210</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2702,7 +2697,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2712,7 +2707,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2731,22 +2726,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Vedyta på död ved</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2764,10 +2759,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121290064</v>
+        <v>121290321</v>
       </c>
       <c r="B18" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2800,7 +2795,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2809,10 +2804,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>619160</v>
+        <v>619129</v>
       </c>
       <c r="R18" t="n">
-        <v>6568210</v>
+        <v>6568209</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2844,7 +2839,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2854,7 +2849,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2873,17 +2868,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 11569-2024 artfynd.xlsx
+++ b/artfynd/A 11569-2024 artfynd.xlsx
@@ -2218,10 +2218,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121289808</v>
+        <v>121288727</v>
       </c>
       <c r="B14" t="n">
-        <v>8435</v>
+        <v>92030</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2230,31 +2230,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2263,10 +2267,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>619177</v>
+        <v>619130</v>
       </c>
       <c r="R14" t="n">
-        <v>6568180</v>
+        <v>6568178</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2298,7 +2302,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2308,7 +2312,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2323,26 +2327,6 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Tallskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2360,10 +2344,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121288727</v>
+        <v>121289808</v>
       </c>
       <c r="B15" t="n">
-        <v>92030</v>
+        <v>8435</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2372,35 +2356,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2409,10 +2389,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>619130</v>
+        <v>619177</v>
       </c>
       <c r="R15" t="n">
-        <v>6568178</v>
+        <v>6568180</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2444,7 +2424,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2454,7 +2434,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2469,6 +2449,26 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Tallskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>

--- a/artfynd/A 11569-2024 artfynd.xlsx
+++ b/artfynd/A 11569-2024 artfynd.xlsx
@@ -1800,7 +1800,7 @@
         <v>121290012</v>
       </c>
       <c r="B11" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1939,10 +1939,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121288667</v>
+        <v>121290254</v>
       </c>
       <c r="B12" t="n">
-        <v>57371</v>
+        <v>4775</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1951,31 +1951,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>619177</v>
+        <v>619160</v>
       </c>
       <c r="R12" t="n">
-        <v>6568180</v>
+        <v>6568210</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2048,22 +2048,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121290064</v>
+        <v>121290321</v>
       </c>
       <c r="B13" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>619160</v>
+        <v>619129</v>
       </c>
       <c r="R13" t="n">
-        <v>6568210</v>
+        <v>6568209</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2190,17 +2190,22 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2218,10 +2223,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121288727</v>
+        <v>121289808</v>
       </c>
       <c r="B14" t="n">
-        <v>92030</v>
+        <v>8435</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2230,35 +2235,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2267,10 +2268,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>619130</v>
+        <v>619177</v>
       </c>
       <c r="R14" t="n">
-        <v>6568178</v>
+        <v>6568180</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2302,7 +2303,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2312,7 +2313,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2327,6 +2328,26 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Tallskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2344,10 +2365,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121289808</v>
+        <v>121288667</v>
       </c>
       <c r="B15" t="n">
-        <v>8435</v>
+        <v>57372</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2356,31 +2377,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2424,7 +2445,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2434,7 +2455,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2463,12 +2484,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Vedyta på död ved</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2489,7 +2510,7 @@
         <v>121288025</v>
       </c>
       <c r="B16" t="n">
-        <v>97061</v>
+        <v>97062</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2617,10 +2638,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121290254</v>
+        <v>121290064</v>
       </c>
       <c r="B17" t="n">
-        <v>4775</v>
+        <v>57372</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2629,31 +2650,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2697,7 +2718,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2707,7 +2728,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2734,14 +2755,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2759,10 +2775,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121290321</v>
+        <v>121288727</v>
       </c>
       <c r="B18" t="n">
-        <v>57371</v>
+        <v>92031</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2775,27 +2791,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2804,10 +2824,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>619129</v>
+        <v>619130</v>
       </c>
       <c r="R18" t="n">
-        <v>6568209</v>
+        <v>6568178</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2839,7 +2859,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2849,7 +2869,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2864,26 +2884,6 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Tallskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 11569-2024 artfynd.xlsx
+++ b/artfynd/A 11569-2024 artfynd.xlsx
@@ -1797,7 +1797,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121290012</v>
+        <v>121288667</v>
       </c>
       <c r="B11" t="n">
         <v>57372</v>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>619161</v>
+        <v>619177</v>
       </c>
       <c r="R11" t="n">
-        <v>6568179</v>
+        <v>6568180</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stump # Pinus sylvestris</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121290254</v>
+        <v>121288025</v>
       </c>
       <c r="B12" t="n">
-        <v>4775</v>
+        <v>97062</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1955,27 +1955,36 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102306</v>
+        <v>221946</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1984,10 +1993,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>619160</v>
+        <v>619193</v>
       </c>
       <c r="R12" t="n">
-        <v>6568210</v>
+        <v>6568180</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2019,7 +2028,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2029,7 +2038,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2044,26 +2053,6 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Tallskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2223,10 +2212,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121289808</v>
+        <v>121290254</v>
       </c>
       <c r="B14" t="n">
-        <v>8435</v>
+        <v>4775</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2239,27 +2228,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>102306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2268,10 +2257,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>619177</v>
+        <v>619160</v>
       </c>
       <c r="R14" t="n">
-        <v>6568180</v>
+        <v>6568210</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2303,7 +2292,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2313,7 +2302,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2332,22 +2321,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Vedyta på död ved</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2365,10 +2354,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121288667</v>
+        <v>121288727</v>
       </c>
       <c r="B15" t="n">
-        <v>57372</v>
+        <v>92031</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2381,27 +2370,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2410,10 +2403,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>619177</v>
+        <v>619130</v>
       </c>
       <c r="R15" t="n">
-        <v>6568180</v>
+        <v>6568178</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2445,7 +2438,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2455,7 +2448,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2470,26 +2463,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Tallskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2507,10 +2480,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121288025</v>
+        <v>121290064</v>
       </c>
       <c r="B16" t="n">
-        <v>97062</v>
+        <v>57372</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2519,40 +2492,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2561,10 +2525,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>619193</v>
+        <v>619160</v>
       </c>
       <c r="R16" t="n">
-        <v>6568180</v>
+        <v>6568210</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2596,7 +2560,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2606,7 +2570,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2621,6 +2585,21 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Tallskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2638,7 +2617,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121290064</v>
+        <v>121290012</v>
       </c>
       <c r="B17" t="n">
         <v>57372</v>
@@ -2683,10 +2662,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>619160</v>
+        <v>619161</v>
       </c>
       <c r="R17" t="n">
-        <v>6568210</v>
+        <v>6568179</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2718,7 +2697,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2728,7 +2707,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2747,17 +2726,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stump # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2775,10 +2759,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121288727</v>
+        <v>121289808</v>
       </c>
       <c r="B18" t="n">
-        <v>92031</v>
+        <v>8435</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2787,35 +2771,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2824,10 +2804,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>619130</v>
+        <v>619177</v>
       </c>
       <c r="R18" t="n">
-        <v>6568178</v>
+        <v>6568180</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2859,7 +2839,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2869,7 +2849,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2884,6 +2864,26 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Tallskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 11569-2024 artfynd.xlsx
+++ b/artfynd/A 11569-2024 artfynd.xlsx
@@ -1797,10 +1797,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121288667</v>
+        <v>121288727</v>
       </c>
       <c r="B11" t="n">
-        <v>57372</v>
+        <v>92031</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1813,27 +1813,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1842,10 +1846,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>619177</v>
+        <v>619130</v>
       </c>
       <c r="R11" t="n">
-        <v>6568180</v>
+        <v>6568178</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1877,7 +1881,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1887,7 +1891,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1902,26 +1906,6 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Tallskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1939,10 +1923,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121288025</v>
+        <v>121290321</v>
       </c>
       <c r="B12" t="n">
-        <v>97062</v>
+        <v>57372</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1951,40 +1935,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1993,10 +1968,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>619193</v>
+        <v>619129</v>
       </c>
       <c r="R12" t="n">
-        <v>6568180</v>
+        <v>6568209</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2028,7 +2003,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2038,7 +2013,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2053,6 +2028,26 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Tallskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2070,10 +2065,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121290321</v>
+        <v>121288025</v>
       </c>
       <c r="B13" t="n">
-        <v>57372</v>
+        <v>97062</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2082,31 +2077,40 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>221946</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2115,10 +2119,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>619129</v>
+        <v>619193</v>
       </c>
       <c r="R13" t="n">
-        <v>6568209</v>
+        <v>6568180</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2150,7 +2154,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2160,7 +2164,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2175,26 +2179,6 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Tallskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2212,10 +2196,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121290254</v>
+        <v>121289808</v>
       </c>
       <c r="B14" t="n">
-        <v>4775</v>
+        <v>8435</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2228,27 +2212,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102306</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2257,10 +2241,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>619160</v>
+        <v>619177</v>
       </c>
       <c r="R14" t="n">
-        <v>6568210</v>
+        <v>6568180</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2292,7 +2276,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2302,7 +2286,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2321,22 +2305,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2354,10 +2338,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121288727</v>
+        <v>121290254</v>
       </c>
       <c r="B15" t="n">
-        <v>92031</v>
+        <v>4775</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2366,35 +2350,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5966</v>
+        <v>102306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2403,10 +2383,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>619130</v>
+        <v>619160</v>
       </c>
       <c r="R15" t="n">
-        <v>6568178</v>
+        <v>6568210</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2438,7 +2418,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2448,7 +2428,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2463,6 +2443,26 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Tallskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2480,7 +2480,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121290064</v>
+        <v>121288667</v>
       </c>
       <c r="B16" t="n">
         <v>57372</v>
@@ -2525,10 +2525,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>619160</v>
+        <v>619177</v>
       </c>
       <c r="R16" t="n">
-        <v>6568210</v>
+        <v>6568180</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2589,17 +2589,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2617,7 +2622,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121290012</v>
+        <v>121290064</v>
       </c>
       <c r="B17" t="n">
         <v>57372</v>
@@ -2662,10 +2667,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>619161</v>
+        <v>619160</v>
       </c>
       <c r="R17" t="n">
-        <v>6568179</v>
+        <v>6568210</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2697,7 +2702,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2707,7 +2712,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2726,22 +2731,17 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Stump # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2759,10 +2759,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121289808</v>
+        <v>121290012</v>
       </c>
       <c r="B18" t="n">
-        <v>8435</v>
+        <v>57372</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2771,31 +2771,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2804,10 +2804,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>619177</v>
+        <v>619161</v>
       </c>
       <c r="R18" t="n">
-        <v>6568180</v>
+        <v>6568179</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Vedyta på död ved</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
+          <t>Stump # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 11569-2024 artfynd.xlsx
+++ b/artfynd/A 11569-2024 artfynd.xlsx
@@ -1923,7 +1923,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121290321</v>
+        <v>121290064</v>
       </c>
       <c r="B12" t="n">
         <v>57372</v>
@@ -1959,7 +1959,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1968,10 +1968,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>619129</v>
+        <v>619160</v>
       </c>
       <c r="R12" t="n">
-        <v>6568209</v>
+        <v>6568210</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2032,22 +2032,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2065,10 +2060,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121288025</v>
+        <v>121289808</v>
       </c>
       <c r="B13" t="n">
-        <v>97062</v>
+        <v>8435</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2081,36 +2076,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221946</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2119,7 +2105,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>619193</v>
+        <v>619177</v>
       </c>
       <c r="R13" t="n">
         <v>6568180</v>
@@ -2154,7 +2140,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2164,7 +2150,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2179,6 +2165,26 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Tallskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2196,10 +2202,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121289808</v>
+        <v>121290254</v>
       </c>
       <c r="B14" t="n">
-        <v>8435</v>
+        <v>4775</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2212,27 +2218,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>102306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2241,10 +2247,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>619177</v>
+        <v>619160</v>
       </c>
       <c r="R14" t="n">
-        <v>6568180</v>
+        <v>6568210</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2276,7 +2282,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2286,7 +2292,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2305,22 +2311,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Vedyta på död ved</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2338,10 +2344,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121290254</v>
+        <v>121288667</v>
       </c>
       <c r="B15" t="n">
-        <v>4775</v>
+        <v>57372</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2350,31 +2356,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2383,10 +2389,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>619160</v>
+        <v>619177</v>
       </c>
       <c r="R15" t="n">
-        <v>6568210</v>
+        <v>6568180</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2418,7 +2424,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2428,7 +2434,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2447,22 +2453,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2480,7 +2486,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121288667</v>
+        <v>121290321</v>
       </c>
       <c r="B16" t="n">
         <v>57372</v>
@@ -2516,7 +2522,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2525,10 +2531,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>619177</v>
+        <v>619129</v>
       </c>
       <c r="R16" t="n">
-        <v>6568180</v>
+        <v>6568209</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2560,7 +2566,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2570,7 +2576,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2622,10 +2628,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121290064</v>
+        <v>121288025</v>
       </c>
       <c r="B17" t="n">
-        <v>57372</v>
+        <v>97062</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2634,31 +2640,40 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>221946</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2667,10 +2682,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>619160</v>
+        <v>619193</v>
       </c>
       <c r="R17" t="n">
-        <v>6568210</v>
+        <v>6568180</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2702,7 +2717,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2712,7 +2727,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2727,21 +2742,6 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Tallskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>

--- a/artfynd/A 11569-2024 artfynd.xlsx
+++ b/artfynd/A 11569-2024 artfynd.xlsx
@@ -1797,10 +1797,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121288727</v>
+        <v>121288667</v>
       </c>
       <c r="B11" t="n">
-        <v>92031</v>
+        <v>57373</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1813,31 +1813,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1846,10 +1842,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>619130</v>
+        <v>619177</v>
       </c>
       <c r="R11" t="n">
-        <v>6568178</v>
+        <v>6568180</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1881,7 +1877,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1891,7 +1887,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1906,6 +1902,26 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Tallskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1923,10 +1939,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121290064</v>
+        <v>121288025</v>
       </c>
       <c r="B12" t="n">
-        <v>57372</v>
+        <v>97067</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1935,31 +1951,40 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>221946</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1968,10 +1993,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>619160</v>
+        <v>619193</v>
       </c>
       <c r="R12" t="n">
-        <v>6568210</v>
+        <v>6568180</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2003,7 +2028,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2013,7 +2038,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2028,21 +2053,6 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Tallskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2060,10 +2070,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121289808</v>
+        <v>121290321</v>
       </c>
       <c r="B13" t="n">
-        <v>8435</v>
+        <v>57373</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2072,31 +2082,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2105,10 +2115,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>619177</v>
+        <v>619129</v>
       </c>
       <c r="R13" t="n">
-        <v>6568180</v>
+        <v>6568209</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2140,7 +2150,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2150,7 +2160,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2179,12 +2189,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Vedyta på död ved</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2205,7 +2215,7 @@
         <v>121290254</v>
       </c>
       <c r="B14" t="n">
-        <v>4775</v>
+        <v>4776</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2344,10 +2354,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121288667</v>
+        <v>121288727</v>
       </c>
       <c r="B15" t="n">
-        <v>57372</v>
+        <v>92036</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2360,27 +2370,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2389,10 +2403,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>619177</v>
+        <v>619130</v>
       </c>
       <c r="R15" t="n">
-        <v>6568180</v>
+        <v>6568178</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2424,7 +2438,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2434,7 +2448,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2449,26 +2463,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Tallskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2486,10 +2480,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121290321</v>
+        <v>121290012</v>
       </c>
       <c r="B16" t="n">
-        <v>57372</v>
+        <v>57373</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2522,7 +2516,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2531,10 +2525,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>619129</v>
+        <v>619161</v>
       </c>
       <c r="R16" t="n">
-        <v>6568209</v>
+        <v>6568179</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2566,7 +2560,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2576,7 +2570,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2605,12 +2599,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Stump # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2628,10 +2622,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121288025</v>
+        <v>121289808</v>
       </c>
       <c r="B17" t="n">
-        <v>97062</v>
+        <v>8436</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2644,36 +2638,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221946</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2682,7 +2667,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>619193</v>
+        <v>619177</v>
       </c>
       <c r="R17" t="n">
         <v>6568180</v>
@@ -2717,7 +2702,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2727,7 +2712,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2742,6 +2727,26 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Tallskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2759,10 +2764,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121290012</v>
+        <v>121290064</v>
       </c>
       <c r="B18" t="n">
-        <v>57372</v>
+        <v>57373</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2804,10 +2809,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>619161</v>
+        <v>619160</v>
       </c>
       <c r="R18" t="n">
-        <v>6568179</v>
+        <v>6568210</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2839,7 +2844,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2849,7 +2854,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2868,22 +2873,17 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stump # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 11569-2024 artfynd.xlsx
+++ b/artfynd/A 11569-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2899,6 +2899,481 @@
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>125368925</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98018</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lundby skog, Lundby skog, Srm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>619193</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6568144</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>125368835</v>
+      </c>
+      <c r="B20" t="n">
+        <v>96979</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lundby skog, Lundby skog, Srm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>619199</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6568171</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>125368693</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98018</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lundby skog, Lundby skog, Srm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>619201</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6568140</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>125368765</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98122</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lundby skog, Lundby skog, Srm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>619195</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6568151</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11569-2024 artfynd.xlsx
+++ b/artfynd/A 11569-2024 artfynd.xlsx
@@ -2901,10 +2901,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125368925</v>
+        <v>125368765</v>
       </c>
       <c r="B19" t="n">
-        <v>98018</v>
+        <v>98122</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2917,26 +2917,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>619193</v>
+        <v>619195</v>
       </c>
       <c r="R19" t="n">
-        <v>6568144</v>
+        <v>6568151</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3134,7 +3134,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125368693</v>
+        <v>125368925</v>
       </c>
       <c r="B21" t="n">
         <v>98018</v>
@@ -3183,10 +3183,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>619201</v>
+        <v>619193</v>
       </c>
       <c r="R21" t="n">
-        <v>6568140</v>
+        <v>6568144</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3255,10 +3255,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125368765</v>
+        <v>125368693</v>
       </c>
       <c r="B22" t="n">
-        <v>98122</v>
+        <v>98018</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3271,26 +3271,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3304,10 +3304,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>619195</v>
+        <v>619201</v>
       </c>
       <c r="R22" t="n">
-        <v>6568151</v>
+        <v>6568140</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 11569-2024 artfynd.xlsx
+++ b/artfynd/A 11569-2024 artfynd.xlsx
@@ -3022,10 +3022,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125368835</v>
+        <v>125368925</v>
       </c>
       <c r="B20" t="n">
-        <v>96979</v>
+        <v>98018</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3038,34 +3038,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lundby skog, Lundby skog, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>619199</v>
+        <v>619193</v>
       </c>
       <c r="R20" t="n">
-        <v>6568171</v>
+        <v>6568144</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3097,7 +3106,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3107,7 +3116,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3134,10 +3143,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125368925</v>
+        <v>125368835</v>
       </c>
       <c r="B21" t="n">
-        <v>98018</v>
+        <v>96979</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3150,43 +3159,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lundby skog, Lundby skog, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>619193</v>
+        <v>619199</v>
       </c>
       <c r="R21" t="n">
-        <v>6568144</v>
+        <v>6568171</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 11569-2024 artfynd.xlsx
+++ b/artfynd/A 11569-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2901,10 +2901,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125368765</v>
+        <v>125368925</v>
       </c>
       <c r="B19" t="n">
-        <v>98122</v>
+        <v>98018</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2917,26 +2917,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>619195</v>
+        <v>619193</v>
       </c>
       <c r="R19" t="n">
-        <v>6568151</v>
+        <v>6568144</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3022,7 +3022,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125368925</v>
+        <v>125368693</v>
       </c>
       <c r="B20" t="n">
         <v>98018</v>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>619193</v>
+        <v>619201</v>
       </c>
       <c r="R20" t="n">
-        <v>6568144</v>
+        <v>6568140</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3255,10 +3255,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125368693</v>
+        <v>125368765</v>
       </c>
       <c r="B22" t="n">
-        <v>98018</v>
+        <v>98122</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3271,26 +3271,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3304,10 +3304,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>619201</v>
+        <v>619195</v>
       </c>
       <c r="R22" t="n">
-        <v>6568140</v>
+        <v>6568151</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3373,6 +3373,945 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>125457619</v>
+      </c>
+      <c r="B23" t="n">
+        <v>95705</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lundby skog, Lundby skog, Srm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>619213</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6568053</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>125457481</v>
+      </c>
+      <c r="B24" t="n">
+        <v>95705</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lundby skog, Lundby skog, Srm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>619216</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6568054</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>125453888</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91032</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lundby skog, Lundby skog, Srm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>619264</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6568144</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>125458389</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98018</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lundby skog, Lundby skog, Srm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>619175</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6568072</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>18:34</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>18:34</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>125457901</v>
+      </c>
+      <c r="B27" t="n">
+        <v>95705</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lundby skog, Lundby skog, Srm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>619211</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6568050</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>18:14</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>18:14</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>125459015</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lundby skog, Lundby skog, Srm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>619208</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6568114</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>18:58</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>18:58</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>125458809</v>
+      </c>
+      <c r="B29" t="n">
+        <v>95705</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lundby skog, Lundby skog, Srm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>619207</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6568092</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>125459089</v>
+      </c>
+      <c r="B30" t="n">
+        <v>96979</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lundby skog, Lundby skog, Srm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>619202</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6568125</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>19:01</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>19:01</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11569-2024 artfynd.xlsx
+++ b/artfynd/A 11569-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2904,7 +2904,7 @@
         <v>125368925</v>
       </c>
       <c r="B19" t="n">
-        <v>98018</v>
+        <v>98186</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>125368693</v>
       </c>
       <c r="B20" t="n">
-        <v>98018</v>
+        <v>98186</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>125368835</v>
       </c>
       <c r="B21" t="n">
-        <v>96979</v>
+        <v>97147</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>125368765</v>
       </c>
       <c r="B22" t="n">
-        <v>98122</v>
+        <v>98290</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3376,10 +3376,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125457619</v>
+        <v>125459015</v>
       </c>
       <c r="B23" t="n">
-        <v>95705</v>
+        <v>57632</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3388,38 +3388,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lundby skog, Lundby skog, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>619213</v>
+        <v>619208</v>
       </c>
       <c r="R23" t="n">
-        <v>6568053</v>
+        <v>6568114</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3451,7 +3456,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3461,7 +3466,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3491,7 +3496,7 @@
         <v>125457481</v>
       </c>
       <c r="B24" t="n">
-        <v>95705</v>
+        <v>95873</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3600,10 +3605,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125453888</v>
+        <v>125459089</v>
       </c>
       <c r="B25" t="n">
-        <v>91032</v>
+        <v>97147</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3612,47 +3617,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lundby skog, Lundby skog, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>619264</v>
+        <v>619202</v>
       </c>
       <c r="R25" t="n">
-        <v>6568144</v>
+        <v>6568125</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3684,7 +3680,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3694,7 +3690,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3705,26 +3701,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Sandbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3741,10 +3717,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125458389</v>
+        <v>125458809</v>
       </c>
       <c r="B26" t="n">
-        <v>98018</v>
+        <v>95873</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3757,46 +3733,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219790</v>
+        <v>2180</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lundby skog, Lundby skog, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>619175</v>
+        <v>619207</v>
       </c>
       <c r="R26" t="n">
-        <v>6568072</v>
+        <v>6568092</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3825,7 +3792,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3835,7 +3802,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3862,10 +3829,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125457901</v>
+        <v>125457619</v>
       </c>
       <c r="B27" t="n">
-        <v>95705</v>
+        <v>95873</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3902,10 +3869,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>619211</v>
+        <v>619213</v>
       </c>
       <c r="R27" t="n">
-        <v>6568050</v>
+        <v>6568053</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3937,7 +3904,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3947,7 +3914,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3974,10 +3941,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125459015</v>
+        <v>125453888</v>
       </c>
       <c r="B28" t="n">
-        <v>57529</v>
+        <v>91186</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3990,27 +3957,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -4019,13 +3990,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>619208</v>
+        <v>619264</v>
       </c>
       <c r="R28" t="n">
-        <v>6568114</v>
+        <v>6568144</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4054,7 +4025,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4064,7 +4035,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4075,6 +4046,26 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -4091,10 +4082,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125458809</v>
+        <v>125457901</v>
       </c>
       <c r="B29" t="n">
-        <v>95705</v>
+        <v>95873</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4131,13 +4122,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>619207</v>
+        <v>619211</v>
       </c>
       <c r="R29" t="n">
-        <v>6568092</v>
+        <v>6568050</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4166,7 +4157,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4176,7 +4167,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4203,10 +4194,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125459089</v>
+        <v>125458389</v>
       </c>
       <c r="B30" t="n">
-        <v>96979</v>
+        <v>98186</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4219,37 +4210,46 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lundby skog, Lundby skog, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>619202</v>
+        <v>619175</v>
       </c>
       <c r="R30" t="n">
-        <v>6568125</v>
+        <v>6568072</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4288,7 +4288,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4312,6 +4312,556 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>125527571</v>
+      </c>
+      <c r="B31" t="n">
+        <v>58001</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lundby skog, Srm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>619199</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6568159</v>
+      </c>
+      <c r="S31" t="n">
+        <v>75</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Björn Carlsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Björn Carlsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>125536996</v>
+      </c>
+      <c r="B32" t="n">
+        <v>97149</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lundby skog, Srm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>619199</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6568159</v>
+      </c>
+      <c r="S32" t="n">
+        <v>75</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Björn Carlsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Björn Carlsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>125527036</v>
+      </c>
+      <c r="B33" t="n">
+        <v>95873</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lundby skog, Srm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>619199</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6568159</v>
+      </c>
+      <c r="S33" t="n">
+        <v>75</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Björn Carlsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Björn Carlsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>125526726</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98290</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lundby skog, Srm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>619199</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6568159</v>
+      </c>
+      <c r="S34" t="n">
+        <v>75</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Björn Carlsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Björn Carlsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>125527972</v>
+      </c>
+      <c r="B35" t="n">
+        <v>58305</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lundby skog, Srm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>619199</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6568159</v>
+      </c>
+      <c r="S35" t="n">
+        <v>75</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Björn Carlsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Björn Carlsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11569-2024 artfynd.xlsx
+++ b/artfynd/A 11569-2024 artfynd.xlsx
@@ -4426,10 +4426,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125536996</v>
+        <v>125527036</v>
       </c>
       <c r="B32" t="n">
-        <v>97149</v>
+        <v>95873</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4442,19 +4442,23 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>224363</v>
+        <v>2180</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
@@ -4529,10 +4533,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125527036</v>
+        <v>125536996</v>
       </c>
       <c r="B33" t="n">
-        <v>95873</v>
+        <v>97149</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4545,23 +4549,19 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2180</v>
+        <v>224363</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>

--- a/artfynd/A 11569-2024 artfynd.xlsx
+++ b/artfynd/A 11569-2024 artfynd.xlsx
@@ -2901,7 +2901,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125368925</v>
+        <v>125368693</v>
       </c>
       <c r="B19" t="n">
         <v>98186</v>
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>619193</v>
+        <v>619201</v>
       </c>
       <c r="R19" t="n">
-        <v>6568144</v>
+        <v>6568140</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3022,10 +3022,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125368693</v>
+        <v>125368835</v>
       </c>
       <c r="B20" t="n">
-        <v>98186</v>
+        <v>97147</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3038,43 +3038,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lundby skog, Lundby skog, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>619201</v>
+        <v>619199</v>
       </c>
       <c r="R20" t="n">
-        <v>6568140</v>
+        <v>6568171</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3106,7 +3097,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3116,7 +3107,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3143,10 +3134,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125368835</v>
+        <v>125368925</v>
       </c>
       <c r="B21" t="n">
-        <v>97147</v>
+        <v>98186</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3159,34 +3150,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lundby skog, Lundby skog, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>619199</v>
+        <v>619193</v>
       </c>
       <c r="R21" t="n">
-        <v>6568171</v>
+        <v>6568144</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3376,10 +3376,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125459015</v>
+        <v>125457619</v>
       </c>
       <c r="B23" t="n">
-        <v>57632</v>
+        <v>95873</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3388,43 +3388,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lundby skog, Lundby skog, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>619208</v>
+        <v>619213</v>
       </c>
       <c r="R23" t="n">
-        <v>6568114</v>
+        <v>6568053</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3456,7 +3451,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3466,7 +3461,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3493,7 +3488,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125457481</v>
+        <v>125458809</v>
       </c>
       <c r="B24" t="n">
         <v>95873</v>
@@ -3533,10 +3528,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>619216</v>
+        <v>619207</v>
       </c>
       <c r="R24" t="n">
-        <v>6568054</v>
+        <v>6568092</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3568,7 +3563,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3578,7 +3573,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3605,10 +3600,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125459089</v>
+        <v>125457901</v>
       </c>
       <c r="B25" t="n">
-        <v>97147</v>
+        <v>95873</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3621,21 +3616,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>2180</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3645,13 +3640,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>619202</v>
+        <v>619211</v>
       </c>
       <c r="R25" t="n">
-        <v>6568125</v>
+        <v>6568050</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3680,7 +3675,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3690,7 +3685,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3717,10 +3712,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125458809</v>
+        <v>125453888</v>
       </c>
       <c r="B26" t="n">
-        <v>95873</v>
+        <v>91186</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3729,38 +3724,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lundby skog, Lundby skog, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>619207</v>
+        <v>619264</v>
       </c>
       <c r="R26" t="n">
-        <v>6568092</v>
+        <v>6568144</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3792,7 +3796,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3802,7 +3806,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3813,6 +3817,26 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3829,10 +3853,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125457619</v>
+        <v>125458389</v>
       </c>
       <c r="B27" t="n">
-        <v>95873</v>
+        <v>98186</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3845,34 +3869,43 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2180</v>
+        <v>219790</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lundby skog, Lundby skog, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>619213</v>
+        <v>619175</v>
       </c>
       <c r="R27" t="n">
-        <v>6568053</v>
+        <v>6568072</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3904,7 +3937,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3914,7 +3947,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3941,10 +3974,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125453888</v>
+        <v>125459015</v>
       </c>
       <c r="B28" t="n">
-        <v>91186</v>
+        <v>57632</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3957,31 +3990,27 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3990,13 +4019,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>619264</v>
+        <v>619208</v>
       </c>
       <c r="R28" t="n">
-        <v>6568144</v>
+        <v>6568114</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4025,7 +4054,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4035,7 +4064,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4046,26 +4075,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Sandbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -4082,10 +4091,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125457901</v>
+        <v>125459089</v>
       </c>
       <c r="B29" t="n">
-        <v>95873</v>
+        <v>97147</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4098,21 +4107,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2180</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4122,13 +4131,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>619211</v>
+        <v>619202</v>
       </c>
       <c r="R29" t="n">
-        <v>6568050</v>
+        <v>6568125</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4157,7 +4166,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4167,7 +4176,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4194,10 +4203,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125458389</v>
+        <v>125457481</v>
       </c>
       <c r="B30" t="n">
-        <v>98186</v>
+        <v>95873</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4210,46 +4219,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219790</v>
+        <v>2180</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lundby skog, Lundby skog, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>619175</v>
+        <v>619216</v>
       </c>
       <c r="R30" t="n">
-        <v>6568072</v>
+        <v>6568054</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4288,7 +4288,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4315,10 +4315,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125527571</v>
+        <v>125526726</v>
       </c>
       <c r="B31" t="n">
-        <v>58001</v>
+        <v>98290</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4331,33 +4331,36 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103015</v>
+        <v>221952</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Lundby skog, Srm</t>
@@ -4408,6 +4411,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4636,10 +4640,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125526726</v>
+        <v>125527972</v>
       </c>
       <c r="B34" t="n">
-        <v>98290</v>
+        <v>58305</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4652,35 +4656,35 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221952</v>
+        <v>103044</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4732,7 +4736,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4751,10 +4754,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125527972</v>
+        <v>125527571</v>
       </c>
       <c r="B35" t="n">
-        <v>58305</v>
+        <v>58001</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4767,16 +4770,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4786,17 +4789,14 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Lundby skog, Srm</t>

--- a/artfynd/A 11569-2024 artfynd.xlsx
+++ b/artfynd/A 11569-2024 artfynd.xlsx
@@ -2901,15 +2901,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125368693</v>
+        <v>125368765</v>
       </c>
       <c r="B19" t="n">
-        <v>98186</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98345</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2917,26 +2912,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2950,10 +2945,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>619201</v>
+        <v>619195</v>
       </c>
       <c r="R19" t="n">
-        <v>6568140</v>
+        <v>6568151</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2985,7 +2980,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2995,7 +2990,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3022,15 +3017,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125368835</v>
+        <v>125368693</v>
       </c>
       <c r="B20" t="n">
-        <v>97147</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98241</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3038,34 +3028,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lundby skog, Lundby skog, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>619199</v>
+        <v>619201</v>
       </c>
       <c r="R20" t="n">
-        <v>6568171</v>
+        <v>6568140</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3097,7 +3096,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3107,7 +3106,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3137,12 +3136,7 @@
         <v>125368925</v>
       </c>
       <c r="B21" t="n">
-        <v>98186</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98241</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3255,15 +3249,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125368765</v>
+        <v>125368835</v>
       </c>
       <c r="B22" t="n">
-        <v>98290</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97202</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3271,43 +3260,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lundby skog, Lundby skog, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>619195</v>
+        <v>619199</v>
       </c>
       <c r="R22" t="n">
-        <v>6568151</v>
+        <v>6568171</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3339,7 +3319,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3349,7 +3329,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3376,15 +3356,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125457619</v>
+        <v>125459089</v>
       </c>
       <c r="B23" t="n">
-        <v>95873</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97202</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3392,21 +3367,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2180</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3416,13 +3391,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>619213</v>
+        <v>619202</v>
       </c>
       <c r="R23" t="n">
-        <v>6568053</v>
+        <v>6568125</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3451,7 +3426,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3461,7 +3436,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3488,15 +3463,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125458809</v>
+        <v>125457901</v>
       </c>
       <c r="B24" t="n">
-        <v>95873</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95927</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3528,13 +3498,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>619207</v>
+        <v>619211</v>
       </c>
       <c r="R24" t="n">
-        <v>6568092</v>
+        <v>6568050</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3563,7 +3533,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3573,7 +3543,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3600,15 +3570,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125457901</v>
+        <v>125457619</v>
       </c>
       <c r="B25" t="n">
-        <v>95873</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95927</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3640,10 +3605,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>619211</v>
+        <v>619213</v>
       </c>
       <c r="R25" t="n">
-        <v>6568050</v>
+        <v>6568053</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3675,7 +3640,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3685,7 +3650,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3712,59 +3677,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125453888</v>
+        <v>125458809</v>
       </c>
       <c r="B26" t="n">
-        <v>91186</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95927</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lundby skog, Lundby skog, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>619264</v>
+        <v>619207</v>
       </c>
       <c r="R26" t="n">
-        <v>6568144</v>
+        <v>6568092</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3796,7 +3747,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3806,7 +3757,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3817,26 +3768,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Sandbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3856,12 +3787,7 @@
         <v>125458389</v>
       </c>
       <c r="B27" t="n">
-        <v>98186</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98241</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3974,58 +3900,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125459015</v>
+        <v>125457481</v>
       </c>
       <c r="B28" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95927</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lundby skog, Lundby skog, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>619208</v>
+        <v>619216</v>
       </c>
       <c r="R28" t="n">
-        <v>6568114</v>
+        <v>6568054</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4054,7 +3970,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4064,7 +3980,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4091,53 +4007,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125459089</v>
+        <v>125459015</v>
       </c>
       <c r="B29" t="n">
-        <v>97147</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lundby skog, Lundby skog, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>619202</v>
+        <v>619208</v>
       </c>
       <c r="R29" t="n">
-        <v>6568125</v>
+        <v>6568114</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4166,7 +4082,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4176,7 +4092,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4203,50 +4119,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125457481</v>
+        <v>125453888</v>
       </c>
       <c r="B30" t="n">
-        <v>95873</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91240</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lundby skog, Lundby skog, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>619216</v>
+        <v>619264</v>
       </c>
       <c r="R30" t="n">
-        <v>6568054</v>
+        <v>6568144</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4278,7 +4198,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4288,7 +4208,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4299,6 +4219,26 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4315,15 +4255,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125526726</v>
+        <v>125536996</v>
       </c>
       <c r="B31" t="n">
-        <v>98290</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97204</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4331,34 +4266,22 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221952</v>
+        <v>224363</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
@@ -4430,15 +4353,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125527036</v>
+        <v>125527972</v>
       </c>
       <c r="B32" t="n">
-        <v>95873</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58325</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4446,27 +4364,35 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2180</v>
+        <v>103044</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4518,7 +4444,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4537,15 +4462,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125536996</v>
+        <v>125526726</v>
       </c>
       <c r="B33" t="n">
-        <v>97149</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98345</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4553,22 +4473,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>224363</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
@@ -4640,15 +4572,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125527972</v>
+        <v>125527571</v>
       </c>
       <c r="B34" t="n">
-        <v>58305</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58019</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4656,16 +4583,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4675,17 +4602,14 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lundby skog, Srm</t>
@@ -4754,15 +4678,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125527571</v>
+        <v>125527036</v>
       </c>
       <c r="B35" t="n">
-        <v>58001</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95927</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4770,33 +4689,28 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Lundby skog, Srm</t>
@@ -4847,6 +4761,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11569-2024 artfynd.xlsx
+++ b/artfynd/A 11569-2024 artfynd.xlsx
@@ -3463,7 +3463,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125457901</v>
+        <v>125457619</v>
       </c>
       <c r="B24" t="n">
         <v>95927</v>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>619211</v>
+        <v>619213</v>
       </c>
       <c r="R24" t="n">
-        <v>6568050</v>
+        <v>6568053</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3570,7 +3570,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125457619</v>
+        <v>125457901</v>
       </c>
       <c r="B25" t="n">
         <v>95927</v>
@@ -3605,10 +3605,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>619213</v>
+        <v>619211</v>
       </c>
       <c r="R25" t="n">
-        <v>6568053</v>
+        <v>6568050</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 11569-2024 artfynd.xlsx
+++ b/artfynd/A 11569-2024 artfynd.xlsx
@@ -2904,7 +2904,7 @@
         <v>125368765</v>
       </c>
       <c r="B19" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>125368693</v>
       </c>
       <c r="B20" t="n">
-        <v>98241</v>
+        <v>98248</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>125368925</v>
       </c>
       <c r="B21" t="n">
-        <v>98241</v>
+        <v>98248</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>125368835</v>
       </c>
       <c r="B22" t="n">
-        <v>97202</v>
+        <v>97209</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>125459089</v>
       </c>
       <c r="B23" t="n">
-        <v>97202</v>
+        <v>97209</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>125457619</v>
       </c>
       <c r="B24" t="n">
-        <v>95927</v>
+        <v>95934</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>125457901</v>
       </c>
       <c r="B25" t="n">
-        <v>95927</v>
+        <v>95934</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>125458809</v>
       </c>
       <c r="B26" t="n">
-        <v>95927</v>
+        <v>95934</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>125458389</v>
       </c>
       <c r="B27" t="n">
-        <v>98241</v>
+        <v>98248</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>125457481</v>
       </c>
       <c r="B28" t="n">
-        <v>95927</v>
+        <v>95934</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>125453888</v>
       </c>
       <c r="B30" t="n">
-        <v>91240</v>
+        <v>91247</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>125536996</v>
       </c>
       <c r="B31" t="n">
-        <v>97204</v>
+        <v>97211</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>125526726</v>
       </c>
       <c r="B33" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>125527036</v>
       </c>
       <c r="B35" t="n">
-        <v>95927</v>
+        <v>95934</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 11569-2024 artfynd.xlsx
+++ b/artfynd/A 11569-2024 artfynd.xlsx
@@ -2904,7 +2904,7 @@
         <v>125368765</v>
       </c>
       <c r="B19" t="n">
-        <v>98352</v>
+        <v>98355</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>125368693</v>
       </c>
       <c r="B20" t="n">
-        <v>98248</v>
+        <v>98251</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>125368925</v>
       </c>
       <c r="B21" t="n">
-        <v>98248</v>
+        <v>98251</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>125368835</v>
       </c>
       <c r="B22" t="n">
-        <v>97209</v>
+        <v>97212</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>125459089</v>
       </c>
       <c r="B23" t="n">
-        <v>97209</v>
+        <v>97212</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>125457619</v>
       </c>
       <c r="B24" t="n">
-        <v>95934</v>
+        <v>95937</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>125457901</v>
       </c>
       <c r="B25" t="n">
-        <v>95934</v>
+        <v>95937</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>125458809</v>
       </c>
       <c r="B26" t="n">
-        <v>95934</v>
+        <v>95937</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>125458389</v>
       </c>
       <c r="B27" t="n">
-        <v>98248</v>
+        <v>98251</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>125457481</v>
       </c>
       <c r="B28" t="n">
-        <v>95934</v>
+        <v>95937</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>125453888</v>
       </c>
       <c r="B30" t="n">
-        <v>91247</v>
+        <v>91248</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>125536996</v>
       </c>
       <c r="B31" t="n">
-        <v>97211</v>
+        <v>97214</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         <v>125527972</v>
       </c>
       <c r="B32" t="n">
-        <v>58325</v>
+        <v>58326</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>125526726</v>
       </c>
       <c r="B33" t="n">
-        <v>98352</v>
+        <v>98355</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>125527571</v>
       </c>
       <c r="B34" t="n">
-        <v>58019</v>
+        <v>58020</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>125527036</v>
       </c>
       <c r="B35" t="n">
-        <v>95934</v>
+        <v>95937</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 11569-2024 artfynd.xlsx
+++ b/artfynd/A 11569-2024 artfynd.xlsx
@@ -2904,7 +2904,7 @@
         <v>125368765</v>
       </c>
       <c r="B19" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>125368693</v>
       </c>
       <c r="B20" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>125368925</v>
       </c>
       <c r="B21" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>125368835</v>
       </c>
       <c r="B22" t="n">
-        <v>97212</v>
+        <v>97216</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>125459089</v>
       </c>
       <c r="B23" t="n">
-        <v>97212</v>
+        <v>97216</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>125457619</v>
       </c>
       <c r="B24" t="n">
-        <v>95937</v>
+        <v>95941</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>125457901</v>
       </c>
       <c r="B25" t="n">
-        <v>95937</v>
+        <v>95941</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>125458809</v>
       </c>
       <c r="B26" t="n">
-        <v>95937</v>
+        <v>95941</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>125458389</v>
       </c>
       <c r="B27" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>125457481</v>
       </c>
       <c r="B28" t="n">
-        <v>95937</v>
+        <v>95941</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>125453888</v>
       </c>
       <c r="B30" t="n">
-        <v>91248</v>
+        <v>91252</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>125536996</v>
       </c>
       <c r="B31" t="n">
-        <v>97214</v>
+        <v>97218</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>125526726</v>
       </c>
       <c r="B33" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>125527036</v>
       </c>
       <c r="B35" t="n">
-        <v>95937</v>
+        <v>95941</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 11569-2024 artfynd.xlsx
+++ b/artfynd/A 11569-2024 artfynd.xlsx
@@ -3900,48 +3900,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125457481</v>
+        <v>125459015</v>
       </c>
       <c r="B28" t="n">
-        <v>95941</v>
+        <v>57648</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lundby skog, Lundby skog, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>619216</v>
+        <v>619208</v>
       </c>
       <c r="R28" t="n">
-        <v>6568054</v>
+        <v>6568114</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3970,7 +3975,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3980,7 +3985,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4007,53 +4012,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125459015</v>
+        <v>125457481</v>
       </c>
       <c r="B29" t="n">
-        <v>57648</v>
+        <v>95941</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lundby skog, Lundby skog, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>619208</v>
+        <v>619216</v>
       </c>
       <c r="R29" t="n">
-        <v>6568114</v>
+        <v>6568054</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 11569-2024 artfynd.xlsx
+++ b/artfynd/A 11569-2024 artfynd.xlsx
@@ -2904,7 +2904,7 @@
         <v>125368765</v>
       </c>
       <c r="B19" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>125368693</v>
       </c>
       <c r="B20" t="n">
-        <v>98255</v>
+        <v>98256</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>125368925</v>
       </c>
       <c r="B21" t="n">
-        <v>98255</v>
+        <v>98256</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>125368835</v>
       </c>
       <c r="B22" t="n">
-        <v>97216</v>
+        <v>97217</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>125459089</v>
       </c>
       <c r="B23" t="n">
-        <v>97216</v>
+        <v>97217</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>125457619</v>
       </c>
       <c r="B24" t="n">
-        <v>95941</v>
+        <v>95942</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>125457901</v>
       </c>
       <c r="B25" t="n">
-        <v>95941</v>
+        <v>95942</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>125458809</v>
       </c>
       <c r="B26" t="n">
-        <v>95941</v>
+        <v>95942</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>125458389</v>
       </c>
       <c r="B27" t="n">
-        <v>98255</v>
+        <v>98256</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>125457481</v>
       </c>
       <c r="B29" t="n">
-        <v>95941</v>
+        <v>95942</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>125536996</v>
       </c>
       <c r="B31" t="n">
-        <v>97218</v>
+        <v>97219</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>125526726</v>
       </c>
       <c r="B33" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>125527036</v>
       </c>
       <c r="B35" t="n">
-        <v>95941</v>
+        <v>95942</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 11569-2024 artfynd.xlsx
+++ b/artfynd/A 11569-2024 artfynd.xlsx
@@ -3900,53 +3900,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125459015</v>
+        <v>125457481</v>
       </c>
       <c r="B28" t="n">
-        <v>57648</v>
+        <v>95942</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lundby skog, Lundby skog, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>619208</v>
+        <v>619216</v>
       </c>
       <c r="R28" t="n">
-        <v>6568114</v>
+        <v>6568054</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3975,7 +3970,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3985,7 +3980,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4012,48 +4007,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125457481</v>
+        <v>125459015</v>
       </c>
       <c r="B29" t="n">
-        <v>95942</v>
+        <v>57648</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lundby skog, Lundby skog, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>619216</v>
+        <v>619208</v>
       </c>
       <c r="R29" t="n">
-        <v>6568054</v>
+        <v>6568114</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 11569-2024 artfynd.xlsx
+++ b/artfynd/A 11569-2024 artfynd.xlsx
@@ -3359,7 +3359,7 @@
         <v>125459089</v>
       </c>
       <c r="B23" t="n">
-        <v>97217</v>
+        <v>97219</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>125457619</v>
       </c>
       <c r="B24" t="n">
-        <v>95942</v>
+        <v>95944</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>125457901</v>
       </c>
       <c r="B25" t="n">
-        <v>95942</v>
+        <v>95944</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>125458809</v>
       </c>
       <c r="B26" t="n">
-        <v>95942</v>
+        <v>95944</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>125458389</v>
       </c>
       <c r="B27" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>125457481</v>
       </c>
       <c r="B28" t="n">
-        <v>95942</v>
+        <v>95944</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>125459015</v>
       </c>
       <c r="B29" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>125453888</v>
       </c>
       <c r="B30" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>125536996</v>
       </c>
       <c r="B31" t="n">
-        <v>97219</v>
+        <v>97221</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         <v>125527972</v>
       </c>
       <c r="B32" t="n">
-        <v>58326</v>
+        <v>58327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>125526726</v>
       </c>
       <c r="B33" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>125527571</v>
       </c>
       <c r="B34" t="n">
-        <v>58020</v>
+        <v>58021</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>125527036</v>
       </c>
       <c r="B35" t="n">
-        <v>95942</v>
+        <v>95944</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 11569-2024 artfynd.xlsx
+++ b/artfynd/A 11569-2024 artfynd.xlsx
@@ -4258,7 +4258,7 @@
         <v>125536996</v>
       </c>
       <c r="B31" t="n">
-        <v>97221</v>
+        <v>97223</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>125526726</v>
       </c>
       <c r="B33" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>125527036</v>
       </c>
       <c r="B35" t="n">
-        <v>95944</v>
+        <v>95946</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
